--- a/BDFotovoltaica.xlsx
+++ b/BDFotovoltaica.xlsx
@@ -503,8 +503,6 @@
       <c r="H2" t="n">
         <v>20.3</v>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>a conferir</t>
@@ -540,8 +538,6 @@
       <c r="H3" t="n">
         <v>21.3</v>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>a conferir</t>
@@ -577,8 +573,6 @@
       <c r="H4" t="n">
         <v>21.5</v>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>a conferir</t>
@@ -614,8 +608,6 @@
       <c r="H5" t="n">
         <v>20.4</v>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>a conferir</t>
@@ -879,7 +871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R17"/>
+  <dimension ref="A1:R47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1212,7 +1204,6 @@
       <c r="I5" t="n">
         <v>25</v>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
         <v>75000</v>
       </c>
@@ -2083,6 +2074,2106 @@
       <c r="R17" t="inlineStr">
         <is>
           <t>GoodWe SMT 50-60kW — en.goodwe.com/Ftp/EN/Downloads/Datasheet/GW_SMT 50-60kW_Datasheet-EN.pdf | potência FV máxima = 130% do nominal CA | no Brasil a potência ativa máxima é 60 kW</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>GW4K-DT</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>GoodWe</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>6000</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E18" t="n">
+        <v>160</v>
+      </c>
+      <c r="F18" t="n">
+        <v>620</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>180V-850V</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4000</v>
+      </c>
+      <c r="L18" t="n">
+        <v>4400</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>50/60Hz</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.8i-0.8c</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>3</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>GoodWe SDT G2 4-15kW — en.goodwe.com/Ftp/EN/Downloads/Datasheet/GW_SDT G2 4-15K_Datasheet-EN.pdf | potência FV máxima = 150% do nominal CA (sobredimensionamento declarado na série)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>GW5K-DT</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>GoodWe</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>7500</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E19" t="n">
+        <v>160</v>
+      </c>
+      <c r="F19" t="n">
+        <v>620</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>180V-850V</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J19" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="K19" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L19" t="n">
+        <v>5500</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>50/60Hz</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>8</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0.8i-0.8c</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>3</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>GoodWe SDT G2 4-15kW — en.goodwe.com/Ftp/EN/Downloads/Datasheet/GW_SDT G2 4-15K_Datasheet-EN.pdf | potência FV máxima = 150% do nominal CA (sobredimensionamento declarado na série)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>GW6K-DT</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>GoodWe</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>9000</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E20" t="n">
+        <v>160</v>
+      </c>
+      <c r="F20" t="n">
+        <v>620</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>180V-850V</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J20" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="K20" t="n">
+        <v>6000</v>
+      </c>
+      <c r="L20" t="n">
+        <v>6600</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>50/60Hz</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>0.8i-0.8c</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>3</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>GoodWe SDT G2 4-15kW — en.goodwe.com/Ftp/EN/Downloads/Datasheet/GW_SDT G2 4-15K_Datasheet-EN.pdf | potência FV máxima = 150% do nominal CA (sobredimensionamento declarado na série)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>GW8K-DT</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>GoodWe</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>12000</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E21" t="n">
+        <v>160</v>
+      </c>
+      <c r="F21" t="n">
+        <v>620</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>180V-850V</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J21" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="K21" t="n">
+        <v>8000</v>
+      </c>
+      <c r="L21" t="n">
+        <v>8800</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>50/60Hz</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>0.8i-0.8c</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>3</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>GoodWe SDT G2 4-15kW — en.goodwe.com/Ftp/EN/Downloads/Datasheet/GW_SDT G2 4-15K_Datasheet-EN.pdf | potência FV máxima = 150% do nominal CA (sobredimensionamento declarado na série)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>GW10KT-DT</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>GoodWe</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E22" t="n">
+        <v>160</v>
+      </c>
+      <c r="F22" t="n">
+        <v>620</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>180V-850V</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J22" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="K22" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L22" t="n">
+        <v>11000</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>50/60Hz</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>16</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>0.8i-0.8c</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>3</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>GoodWe SDT G2 4-15kW — en.goodwe.com/Ftp/EN/Downloads/Datasheet/GW_SDT G2 4-15K_Datasheet-EN.pdf | potência FV máxima = 150% do nominal CA (sobredimensionamento declarado na série)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>GW12KT-DT</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>GoodWe</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>18000</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E23" t="n">
+        <v>160</v>
+      </c>
+      <c r="F23" t="n">
+        <v>620</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>180V-850V</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J23" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="K23" t="n">
+        <v>12000</v>
+      </c>
+      <c r="L23" t="n">
+        <v>13200</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>50/60Hz</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>0.8i-0.8c</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>3</v>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>GoodWe SDT G2 4-15kW — en.goodwe.com/Ftp/EN/Downloads/Datasheet/GW_SDT G2 4-15K_Datasheet-EN.pdf | potência FV máxima = 150% do nominal CA (sobredimensionamento declarado na série) | correntes por MPPT 25 / 12,5 A; a menor governa o arranjo</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>GW15KT-DT</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>GoodWe</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>22500</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E24" t="n">
+        <v>160</v>
+      </c>
+      <c r="F24" t="n">
+        <v>620</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>180V-850V</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J24" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="K24" t="n">
+        <v>15000</v>
+      </c>
+      <c r="L24" t="n">
+        <v>16500</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>50/60Hz</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>24</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>0.8i-0.8c</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>3</v>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>GoodWe SDT G2 4-15kW — en.goodwe.com/Ftp/EN/Downloads/Datasheet/GW_SDT G2 4-15K_Datasheet-EN.pdf | potência FV máxima = 150% do nominal CA (sobredimensionamento declarado na série) | correntes por MPPT 25 / 12,5 A; a menor governa o arranjo</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>GW17KT-DT</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>GoodWe</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>25500</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E25" t="n">
+        <v>180</v>
+      </c>
+      <c r="F25" t="n">
+        <v>620</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>200V-950V</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" t="n">
+        <v>25</v>
+      </c>
+      <c r="J25" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="K25" t="n">
+        <v>17000</v>
+      </c>
+      <c r="L25" t="n">
+        <v>19000</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>50/60Hz</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>0.8i-0.8c</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>3</v>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>GoodWe SDT G2 17-25kW — en.goodwe.com/Ftp/EN/Downloads/Datasheet/GW_SDT G2 17-25K_Datasheet-EN.pdf | potência FV máxima = 150% do nominal CA (sobredimensionamento declarado na série)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>GW20KT-DT</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>GoodWe</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E26" t="n">
+        <v>180</v>
+      </c>
+      <c r="F26" t="n">
+        <v>620</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>200V-950V</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" t="n">
+        <v>25</v>
+      </c>
+      <c r="J26" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="K26" t="n">
+        <v>20000</v>
+      </c>
+      <c r="L26" t="n">
+        <v>22000</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>50/60Hz</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>0.8i-0.8c</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>3</v>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>GoodWe SDT G2 17-25kW — en.goodwe.com/Ftp/EN/Downloads/Datasheet/GW_SDT G2 17-25K_Datasheet-EN.pdf | potência FV máxima = 150% do nominal CA (sobredimensionamento declarado na série)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>GW25KT-DT</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>GoodWe</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>37500</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E27" t="n">
+        <v>180</v>
+      </c>
+      <c r="F27" t="n">
+        <v>620</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>200V-950V</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>2</v>
+      </c>
+      <c r="I27" t="n">
+        <v>25</v>
+      </c>
+      <c r="J27" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="K27" t="n">
+        <v>25000</v>
+      </c>
+      <c r="L27" t="n">
+        <v>27500</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>50/60Hz</t>
+        </is>
+      </c>
+      <c r="O27" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>0.8i-0.8c</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>3</v>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>GoodWe SDT G2 17-25kW — en.goodwe.com/Ftp/EN/Downloads/Datasheet/GW_SDT G2 17-25K_Datasheet-EN.pdf | potência FV máxima = 150% do nominal CA (sobredimensionamento declarado na série) | correntes por MPPT 37,5 / 25 A; a menor governa o arranjo</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>GW25K-MT</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>GoodWe</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>32500</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E28" t="n">
+        <v>180</v>
+      </c>
+      <c r="F28" t="n">
+        <v>600</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>200V-950V</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>3</v>
+      </c>
+      <c r="I28" t="n">
+        <v>30</v>
+      </c>
+      <c r="J28" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="K28" t="n">
+        <v>25000</v>
+      </c>
+      <c r="L28" t="n">
+        <v>27500</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>50/60Hz</t>
+        </is>
+      </c>
+      <c r="O28" t="n">
+        <v>40</v>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>0.8i-0.8c</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>3</v>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>GoodWe SMT 25-36kW — en.goodwe.com/Ftp/EN/Downloads/Datasheet/GW_SMT 15A_Datasheet-EN.pdf | potência FV máxima = 130% do nominal CA (sobredimensionamento declarado na série)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>GW29.9K-MT</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>GoodWe</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>38870</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E29" t="n">
+        <v>180</v>
+      </c>
+      <c r="F29" t="n">
+        <v>600</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>200V-950V</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>3</v>
+      </c>
+      <c r="I29" t="n">
+        <v>30</v>
+      </c>
+      <c r="J29" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="K29" t="n">
+        <v>29900</v>
+      </c>
+      <c r="L29" t="n">
+        <v>29900</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>50/60Hz</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>0.8i-0.8c</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>3</v>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>GoodWe SMT 25-36kW — en.goodwe.com/Ftp/EN/Downloads/Datasheet/GW_SMT 15A_Datasheet-EN.pdf | potência FV máxima = 130% do nominal CA (sobredimensionamento declarado na série)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>GW30K-MT</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>GoodWe</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>39000</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E30" t="n">
+        <v>180</v>
+      </c>
+      <c r="F30" t="n">
+        <v>600</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>200V-950V</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>3</v>
+      </c>
+      <c r="I30" t="n">
+        <v>30</v>
+      </c>
+      <c r="J30" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="K30" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L30" t="n">
+        <v>33000</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>50/60Hz</t>
+        </is>
+      </c>
+      <c r="O30" t="n">
+        <v>48</v>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>0.8i-0.8c</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>3</v>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>GoodWe SMT 25-36kW — en.goodwe.com/Ftp/EN/Downloads/Datasheet/GW_SMT 15A_Datasheet-EN.pdf | potência FV máxima = 130% do nominal CA (sobredimensionamento declarado na série)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>GW36K-MT</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>GoodWe</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>46800</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E31" t="n">
+        <v>180</v>
+      </c>
+      <c r="F31" t="n">
+        <v>600</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>200V-950V</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>3</v>
+      </c>
+      <c r="I31" t="n">
+        <v>30</v>
+      </c>
+      <c r="J31" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="K31" t="n">
+        <v>36000</v>
+      </c>
+      <c r="L31" t="n">
+        <v>36000</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>50/60Hz</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>0.8i-0.8c</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>3</v>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>GoodWe SMT 25-36kW — en.goodwe.com/Ftp/EN/Downloads/Datasheet/GW_SMT 15A_Datasheet-EN.pdf | potência FV máxima = 130% do nominal CA (sobredimensionamento declarado na série)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>GW30KLV-MT</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>GoodWe</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>54000</v>
+      </c>
+      <c r="D32" t="n">
+        <v>800</v>
+      </c>
+      <c r="E32" t="n">
+        <v>200</v>
+      </c>
+      <c r="F32" t="n">
+        <v>370</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>200V-650V</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>4</v>
+      </c>
+      <c r="I32" t="n">
+        <v>22</v>
+      </c>
+      <c r="J32" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="K32" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L32" t="n">
+        <v>33000</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>50/60Hz</t>
+        </is>
+      </c>
+      <c r="O32" t="n">
+        <v>80</v>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>0.8i-0.8c</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>3</v>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>GoodWe LVMT 30-50kW — en.goodwe.com/Ftp/EN/Downloads/Datasheet/GW_LVMT_Datasheet-EN.pdf | potência FV máxima = 180% do nominal CA (sobredimensionamento declarado na série) | correntes por MPPT 33 / 33 / 22 / 22 A; a menor governa o arranjo</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>GW35KLV-MT</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>GoodWe</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>64800</v>
+      </c>
+      <c r="D33" t="n">
+        <v>800</v>
+      </c>
+      <c r="E33" t="n">
+        <v>200</v>
+      </c>
+      <c r="F33" t="n">
+        <v>370</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>200V-650V</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>4</v>
+      </c>
+      <c r="I33" t="n">
+        <v>33</v>
+      </c>
+      <c r="J33" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="K33" t="n">
+        <v>36000</v>
+      </c>
+      <c r="L33" t="n">
+        <v>39900</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>50/60Hz</t>
+        </is>
+      </c>
+      <c r="O33" t="n">
+        <v>96</v>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>0.8i-0.8c</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>3</v>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>GoodWe LVMT 30-50kW — en.goodwe.com/Ftp/EN/Downloads/Datasheet/GW_LVMT_Datasheet-EN.pdf | potência FV máxima = 180% do nominal CA (sobredimensionamento declarado na série)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>GW4000-SDT-30</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>GoodWe</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>6000</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E34" t="n">
+        <v>160</v>
+      </c>
+      <c r="F34" t="n">
+        <v>600</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>140V-1000V</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I34" t="n">
+        <v>22</v>
+      </c>
+      <c r="J34" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="K34" t="n">
+        <v>4000</v>
+      </c>
+      <c r="L34" t="n">
+        <v>4400</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>220/380 ou 230/400</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>50/60Hz</t>
+        </is>
+      </c>
+      <c r="O34" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>0.8i-0.8c</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>3</v>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>GoodWe SDT G3 4-30kW — en.goodwe.com/Ftp/EN/Downloads/Datasheet/GW_SDT-G3_Datasheet-EN.pdf | potência FV máxima = 150% do nominal CA (sobredimensionamento declarado na série)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>GW5000-SDT-30</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>GoodWe</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>7500</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E35" t="n">
+        <v>160</v>
+      </c>
+      <c r="F35" t="n">
+        <v>600</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>140V-1000V</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>2</v>
+      </c>
+      <c r="I35" t="n">
+        <v>22</v>
+      </c>
+      <c r="J35" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="K35" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L35" t="n">
+        <v>5500</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>220/380 ou 230/400</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>50/60Hz</t>
+        </is>
+      </c>
+      <c r="O35" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>0.8i-0.8c</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>3</v>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>GoodWe SDT G3 4-30kW — en.goodwe.com/Ftp/EN/Downloads/Datasheet/GW_SDT-G3_Datasheet-EN.pdf | potência FV máxima = 150% do nominal CA (sobredimensionamento declarado na série)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>GW6000-SDT-30</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>GoodWe</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>9000</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E36" t="n">
+        <v>160</v>
+      </c>
+      <c r="F36" t="n">
+        <v>600</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>140V-1000V</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>2</v>
+      </c>
+      <c r="I36" t="n">
+        <v>22</v>
+      </c>
+      <c r="J36" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="K36" t="n">
+        <v>6000</v>
+      </c>
+      <c r="L36" t="n">
+        <v>6600</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>220/380 ou 230/400</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>50/60Hz</t>
+        </is>
+      </c>
+      <c r="O36" t="n">
+        <v>10</v>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>0.8i-0.8c</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>3</v>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>GoodWe SDT G3 4-30kW — en.goodwe.com/Ftp/EN/Downloads/Datasheet/GW_SDT-G3_Datasheet-EN.pdf | potência FV máxima = 150% do nominal CA (sobredimensionamento declarado na série)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>GW8000-SDT-30</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>GoodWe</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>12000</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E37" t="n">
+        <v>160</v>
+      </c>
+      <c r="F37" t="n">
+        <v>600</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>140V-1000V</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>2</v>
+      </c>
+      <c r="I37" t="n">
+        <v>22</v>
+      </c>
+      <c r="J37" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="K37" t="n">
+        <v>8000</v>
+      </c>
+      <c r="L37" t="n">
+        <v>8800</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>220/380 ou 230/400</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>50/60Hz</t>
+        </is>
+      </c>
+      <c r="O37" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>0.8i-0.8c</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>3</v>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>GoodWe SDT G3 4-30kW — en.goodwe.com/Ftp/EN/Downloads/Datasheet/GW_SDT-G3_Datasheet-EN.pdf | potência FV máxima = 150% do nominal CA (sobredimensionamento declarado na série)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>GW10K-SDT-30</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>GoodWe</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E38" t="n">
+        <v>160</v>
+      </c>
+      <c r="F38" t="n">
+        <v>600</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>140V-1000V</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>2</v>
+      </c>
+      <c r="I38" t="n">
+        <v>22</v>
+      </c>
+      <c r="J38" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="K38" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L38" t="n">
+        <v>11000</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>220/380 ou 230/400</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>50/60Hz</t>
+        </is>
+      </c>
+      <c r="O38" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>0.8i-0.8c</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>3</v>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>GoodWe SDT G3 4-30kW — en.goodwe.com/Ftp/EN/Downloads/Datasheet/GW_SDT-G3_Datasheet-EN.pdf | potência FV máxima = 150% do nominal CA (sobredimensionamento declarado na série)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>GW12K-SDT-30</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>GoodWe</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>18000</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E39" t="n">
+        <v>160</v>
+      </c>
+      <c r="F39" t="n">
+        <v>600</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>140V-1000V</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>2</v>
+      </c>
+      <c r="I39" t="n">
+        <v>22</v>
+      </c>
+      <c r="J39" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="K39" t="n">
+        <v>12000</v>
+      </c>
+      <c r="L39" t="n">
+        <v>13200</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>220/380 ou 230/400</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>50/60Hz</t>
+        </is>
+      </c>
+      <c r="O39" t="n">
+        <v>20</v>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>0.8i-0.8c</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>3</v>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>GoodWe SDT G3 4-30kW — en.goodwe.com/Ftp/EN/Downloads/Datasheet/GW_SDT-G3_Datasheet-EN.pdf | potência FV máxima = 150% do nominal CA (sobredimensionamento declarado na série)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>GW15K-SDT-30</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>GoodWe</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>22500</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E40" t="n">
+        <v>160</v>
+      </c>
+      <c r="F40" t="n">
+        <v>600</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>140V-1000V</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>2</v>
+      </c>
+      <c r="I40" t="n">
+        <v>22</v>
+      </c>
+      <c r="J40" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="K40" t="n">
+        <v>15000</v>
+      </c>
+      <c r="L40" t="n">
+        <v>16500</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>220/380 ou 230/400</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>50/60Hz</t>
+        </is>
+      </c>
+      <c r="O40" t="n">
+        <v>25</v>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>0.8i-0.8c</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>3</v>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>GoodWe SDT G3 4-30kW — en.goodwe.com/Ftp/EN/Downloads/Datasheet/GW_SDT-G3_Datasheet-EN.pdf | potência FV máxima = 150% do nominal CA (sobredimensionamento declarado na série)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>GW17K-SDT-30</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>GoodWe</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>25500</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E41" t="n">
+        <v>160</v>
+      </c>
+      <c r="F41" t="n">
+        <v>600</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>140V-1000V</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I41" t="n">
+        <v>22</v>
+      </c>
+      <c r="J41" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="K41" t="n">
+        <v>17000</v>
+      </c>
+      <c r="L41" t="n">
+        <v>18700</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>220/380 ou 230/400</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>50/60Hz</t>
+        </is>
+      </c>
+      <c r="O41" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>0.8i-0.8c</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>3</v>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>GoodWe SDT G3 4-30kW — en.goodwe.com/Ftp/EN/Downloads/Datasheet/GW_SDT-G3_Datasheet-EN.pdf | potência FV máxima = 150% do nominal CA (sobredimensionamento declarado na série) | correntes por MPPT 32 / 22 A; a menor governa o arranjo</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>GW20K-SDT-30</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>GoodWe</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E42" t="n">
+        <v>160</v>
+      </c>
+      <c r="F42" t="n">
+        <v>600</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>140V-1000V</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>2</v>
+      </c>
+      <c r="I42" t="n">
+        <v>22</v>
+      </c>
+      <c r="J42" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="K42" t="n">
+        <v>20000</v>
+      </c>
+      <c r="L42" t="n">
+        <v>22000</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>220/380 ou 230/400</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>50/60Hz</t>
+        </is>
+      </c>
+      <c r="O42" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>0.8i-0.8c</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>3</v>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>GoodWe SDT G3 4-30kW — en.goodwe.com/Ftp/EN/Downloads/Datasheet/GW_SDT-G3_Datasheet-EN.pdf | potência FV máxima = 150% do nominal CA (sobredimensionamento declarado na série) | correntes por MPPT 32 / 22 A; a menor governa o arranjo</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>GW25K-SDT-30</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>GoodWe</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>37500</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E43" t="n">
+        <v>160</v>
+      </c>
+      <c r="F43" t="n">
+        <v>600</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>140V-1000V</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>3</v>
+      </c>
+      <c r="I43" t="n">
+        <v>40</v>
+      </c>
+      <c r="J43" t="n">
+        <v>50</v>
+      </c>
+      <c r="K43" t="n">
+        <v>25000</v>
+      </c>
+      <c r="L43" t="n">
+        <v>25000</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>220/380 ou 230/400</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>50/60Hz</t>
+        </is>
+      </c>
+      <c r="O43" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>0.8i-0.8c</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>3</v>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>GoodWe SDT G3 4-30kW — en.goodwe.com/Ftp/EN/Downloads/Datasheet/GW_SDT-G3_Datasheet-EN.pdf | potência FV máxima = 150% do nominal CA (sobredimensionamento declarado na série)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>GW12KLV-SDT-C30</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>GoodWe</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>18000</v>
+      </c>
+      <c r="D44" t="n">
+        <v>850</v>
+      </c>
+      <c r="E44" t="n">
+        <v>160</v>
+      </c>
+      <c r="F44" t="n">
+        <v>420</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>140V-700V</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>2</v>
+      </c>
+      <c r="I44" t="n">
+        <v>22</v>
+      </c>
+      <c r="J44" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="K44" t="n">
+        <v>12000</v>
+      </c>
+      <c r="L44" t="n">
+        <v>13200</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>127/220</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>60Hz</t>
+        </is>
+      </c>
+      <c r="O44" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>0.8i-0.8c</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>3</v>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>GoodWe SDT G3 4-30kW — en.goodwe.com/Ftp/EN/Downloads/Datasheet/GW_SDT-G3_Datasheet-EN.pdf | potência FV máxima = 150% do nominal CA (sobredimensionamento declarado na série) | saída 127/220 V em 60 Hz (linha LV, mercado brasileiro) | correntes por MPPT 32 / 22 A; a menor governa o arranjo</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>GW17KLV-SDT-C30</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>GoodWe</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>25500</v>
+      </c>
+      <c r="D45" t="n">
+        <v>850</v>
+      </c>
+      <c r="E45" t="n">
+        <v>160</v>
+      </c>
+      <c r="F45" t="n">
+        <v>420</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>140V-700V</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>2</v>
+      </c>
+      <c r="I45" t="n">
+        <v>32</v>
+      </c>
+      <c r="J45" t="n">
+        <v>40</v>
+      </c>
+      <c r="K45" t="n">
+        <v>17000</v>
+      </c>
+      <c r="L45" t="n">
+        <v>18700</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>127/220</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>60Hz</t>
+        </is>
+      </c>
+      <c r="O45" t="n">
+        <v>50</v>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>0.8i-0.8c</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>3</v>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>GoodWe SDT G3 4-30kW — en.goodwe.com/Ftp/EN/Downloads/Datasheet/GW_SDT-G3_Datasheet-EN.pdf | potência FV máxima = 150% do nominal CA (sobredimensionamento declarado na série) | saída 127/220 V em 60 Hz (linha LV, mercado brasileiro) | correntes por MPPT 42 / 32 A; a menor governa o arranjo</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>GW23KLV-SDT-BR30</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>GoodWe</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>34500</v>
+      </c>
+      <c r="D46" t="n">
+        <v>850</v>
+      </c>
+      <c r="E46" t="n">
+        <v>160</v>
+      </c>
+      <c r="F46" t="n">
+        <v>420</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>140V-700V</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>3</v>
+      </c>
+      <c r="I46" t="n">
+        <v>32</v>
+      </c>
+      <c r="J46" t="n">
+        <v>40</v>
+      </c>
+      <c r="K46" t="n">
+        <v>23000</v>
+      </c>
+      <c r="L46" t="n">
+        <v>25300</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>127/220</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>60Hz</t>
+        </is>
+      </c>
+      <c r="O46" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>0.8i-0.8c</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>3</v>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>GoodWe SDT G3 4-30kW — en.goodwe.com/Ftp/EN/Downloads/Datasheet/GW_SDT-G3_Datasheet-EN.pdf | potência FV máxima = 150% do nominal CA (sobredimensionamento declarado na série) | saída 127/220 V em 60 Hz (linha LV, mercado brasileiro) | correntes por MPPT 42 / 42 / 32 A; a menor governa o arranjo</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>GW30KLV-SDT-C30</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>GoodWe</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>45000</v>
+      </c>
+      <c r="D47" t="n">
+        <v>850</v>
+      </c>
+      <c r="E47" t="n">
+        <v>160</v>
+      </c>
+      <c r="F47" t="n">
+        <v>420</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>140V-700V</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>4</v>
+      </c>
+      <c r="I47" t="n">
+        <v>40</v>
+      </c>
+      <c r="J47" t="n">
+        <v>52</v>
+      </c>
+      <c r="K47" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L47" t="n">
+        <v>33000</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>127/220</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>60Hz</t>
+        </is>
+      </c>
+      <c r="O47" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.8i-0.8c</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>3</v>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>GoodWe SDT G3 4-30kW — en.goodwe.com/Ftp/EN/Downloads/Datasheet/GW_SDT-G3_Datasheet-EN.pdf | potência FV máxima = 150% do nominal CA (sobredimensionamento declarado na série) | saída 127/220 V em 60 Hz (linha LV, mercado brasileiro)</t>
         </is>
       </c>
     </row>
